--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/47.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/47.xlsx
@@ -426,13 +426,13 @@
         <v>1.71635026700038</v>
       </c>
       <c r="E2">
-        <v>-6.318292037273561</v>
+        <v>-8.100839789386852</v>
       </c>
       <c r="F2">
-        <v>-7.870842461553812</v>
+        <v>-8.355506754341098</v>
       </c>
       <c r="G2">
-        <v>-6.938566925335737</v>
+        <v>-7.376810322733378</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>2.245101578229133</v>
       </c>
       <c r="E3">
-        <v>-7.108678305150322</v>
+        <v>-8.355167946605635</v>
       </c>
       <c r="F3">
-        <v>-7.667013175413093</v>
+        <v>-7.966274996312277</v>
       </c>
       <c r="G3">
-        <v>-6.758479869090462</v>
+        <v>-7.541298088397606</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>2.605757489211035</v>
       </c>
       <c r="E4">
-        <v>-7.934717248889472</v>
+        <v>-9.163876420317429</v>
       </c>
       <c r="F4">
-        <v>-7.642899669144612</v>
+        <v>-7.757269763313424</v>
       </c>
       <c r="G4">
-        <v>-6.611468473328046</v>
+        <v>-7.834940167185421</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>2.718170440531744</v>
       </c>
       <c r="E5">
-        <v>-8.346898953067628</v>
+        <v>-8.306151743946611</v>
       </c>
       <c r="F5">
-        <v>-7.481213193340216</v>
+        <v>-8.134397257030541</v>
       </c>
       <c r="G5">
-        <v>-7.18842372882115</v>
+        <v>-7.93973879677659</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>2.613561219484024</v>
       </c>
       <c r="E6">
-        <v>-8.911210213059462</v>
+        <v>-9.890085154557486</v>
       </c>
       <c r="F6">
-        <v>-7.208074601516206</v>
+        <v>-7.703940446243394</v>
       </c>
       <c r="G6">
-        <v>-7.098949614531268</v>
+        <v>-8.080201933462327</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>2.317252561126231</v>
       </c>
       <c r="E7">
-        <v>-9.172788457164524</v>
+        <v>-8.57253922744782</v>
       </c>
       <c r="F7">
-        <v>-7.468524541545715</v>
+        <v>-7.414209763469803</v>
       </c>
       <c r="G7">
-        <v>-7.464854281350295</v>
+        <v>-9.164091095747409</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>1.882867402993873</v>
       </c>
       <c r="E8">
-        <v>-10.05074635540162</v>
+        <v>-10.40164874930798</v>
       </c>
       <c r="F8">
-        <v>-7.26114141933075</v>
+        <v>-7.539146343506427</v>
       </c>
       <c r="G8">
-        <v>-8.645414683927635</v>
+        <v>-9.946915936145631</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.371369280452132</v>
       </c>
       <c r="E9">
-        <v>-11.14878356193748</v>
+        <v>-11.97888907533552</v>
       </c>
       <c r="F9">
-        <v>-7.030037153987855</v>
+        <v>-7.532303150245814</v>
       </c>
       <c r="G9">
-        <v>-8.415758829322854</v>
+        <v>-9.433850899014923</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.8533021769102161</v>
       </c>
       <c r="E10">
-        <v>-11.40361890824512</v>
+        <v>-11.99061329454137</v>
       </c>
       <c r="F10">
-        <v>-6.793064070448819</v>
+        <v>-7.006852491238779</v>
       </c>
       <c r="G10">
-        <v>-9.260437902576818</v>
+        <v>-9.53179007824872</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.3931192224944076</v>
       </c>
       <c r="E11">
-        <v>-11.45062446844474</v>
+        <v>-12.43315388846695</v>
       </c>
       <c r="F11">
-        <v>-6.555800772800779</v>
+        <v>-7.248705368629762</v>
       </c>
       <c r="G11">
-        <v>-9.287375811629868</v>
+        <v>-9.856508248013675</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.04701081047388037</v>
       </c>
       <c r="E12">
-        <v>-11.49729039309378</v>
+        <v>-12.77933308398331</v>
       </c>
       <c r="F12">
-        <v>-6.722033276435445</v>
+        <v>-7.111583755279747</v>
       </c>
       <c r="G12">
-        <v>-9.468386510080599</v>
+        <v>-10.90570951413827</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.1498798806280428</v>
       </c>
       <c r="E13">
-        <v>-12.37629889730065</v>
+        <v>-13.48143222260653</v>
       </c>
       <c r="F13">
-        <v>-6.381652115147791</v>
+        <v>-6.964078178168675</v>
       </c>
       <c r="G13">
-        <v>-9.875686238322674</v>
+        <v>-11.06760181209971</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.1774921558006418</v>
       </c>
       <c r="E14">
-        <v>-12.59286863824348</v>
+        <v>-14.11454911667091</v>
       </c>
       <c r="F14">
-        <v>-6.098763437855377</v>
+        <v>-6.630426579242202</v>
       </c>
       <c r="G14">
-        <v>-9.647967052858364</v>
+        <v>-10.75244118730664</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.04082385025027793</v>
       </c>
       <c r="E15">
-        <v>-13.90538343073062</v>
+        <v>-14.06605821699678</v>
       </c>
       <c r="F15">
-        <v>-6.066649049302096</v>
+        <v>-6.405822634829227</v>
       </c>
       <c r="G15">
-        <v>-9.33601434669284</v>
+        <v>-9.522288812551013</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.2362802629729991</v>
       </c>
       <c r="E16">
-        <v>-13.97772127452915</v>
+        <v>-13.84634118661862</v>
       </c>
       <c r="F16">
-        <v>-5.65959782823923</v>
+        <v>-6.384481009839244</v>
       </c>
       <c r="G16">
-        <v>-8.806492587686414</v>
+        <v>-9.299065347929035</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.6117619089244131</v>
       </c>
       <c r="E17">
-        <v>-13.92622799658793</v>
+        <v>-15.3851755245871</v>
       </c>
       <c r="F17">
-        <v>-5.340921356522673</v>
+        <v>-6.025583554914751</v>
       </c>
       <c r="G17">
-        <v>-8.838409557230529</v>
+        <v>-9.313065645014612</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.030407910271917</v>
       </c>
       <c r="E18">
-        <v>-14.73956004226156</v>
+        <v>-17.44125669218571</v>
       </c>
       <c r="F18">
-        <v>-5.148025184169191</v>
+        <v>-5.949435015235633</v>
       </c>
       <c r="G18">
-        <v>-8.459070696613139</v>
+        <v>-9.157268061390972</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.436988899826226</v>
       </c>
       <c r="E19">
-        <v>-16.30906120620999</v>
+        <v>-16.24415005978404</v>
       </c>
       <c r="F19">
-        <v>-4.508300641127707</v>
+        <v>-5.189161153469772</v>
       </c>
       <c r="G19">
-        <v>-8.066651870570089</v>
+        <v>-7.759211437974592</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.77998374548555</v>
       </c>
       <c r="E20">
-        <v>-16.64200820067594</v>
+        <v>-18.09365582857475</v>
       </c>
       <c r="F20">
-        <v>-4.06787440160287</v>
+        <v>-4.997515316936529</v>
       </c>
       <c r="G20">
-        <v>-7.744343777957726</v>
+        <v>-7.929303957236806</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.020077840694054</v>
       </c>
       <c r="E21">
-        <v>-17.78265834762398</v>
+        <v>-18.78978643845586</v>
       </c>
       <c r="F21">
-        <v>-3.781492860913954</v>
+        <v>-4.776056216545139</v>
       </c>
       <c r="G21">
-        <v>-7.396253156685517</v>
+        <v>-8.280334342947887</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.132228489012301</v>
       </c>
       <c r="E22">
-        <v>-18.15579102043399</v>
+        <v>-18.39277059372939</v>
       </c>
       <c r="F22">
-        <v>-3.376721384516363</v>
+        <v>-4.23007360219739</v>
       </c>
       <c r="G22">
-        <v>-7.467049173042832</v>
+        <v>-7.919736480628313</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.107022057621871</v>
       </c>
       <c r="E23">
-        <v>-19.13715209416223</v>
+        <v>-20.3203925391524</v>
       </c>
       <c r="F23">
-        <v>-3.401693259391013</v>
+        <v>-3.945719205080237</v>
       </c>
       <c r="G23">
-        <v>-6.879238638726457</v>
+        <v>-7.214808776769142</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.950753015923088</v>
       </c>
       <c r="E24">
-        <v>-18.58374539958086</v>
+        <v>-19.48354865643095</v>
       </c>
       <c r="F24">
-        <v>-2.927541210543934</v>
+        <v>-4.048322760223813</v>
       </c>
       <c r="G24">
-        <v>-7.080013294046637</v>
+        <v>-7.704309350751319</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.683444635711325</v>
       </c>
       <c r="E25">
-        <v>-20.09349787747209</v>
+        <v>-20.97253355252301</v>
       </c>
       <c r="F25">
-        <v>-2.915487624821525</v>
+        <v>-3.56014620364256</v>
       </c>
       <c r="G25">
-        <v>-7.403476767052207</v>
+        <v>-7.958377168162686</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.336658055890417</v>
       </c>
       <c r="E26">
-        <v>-19.45936207675599</v>
+        <v>-21.23111394683499</v>
       </c>
       <c r="F26">
-        <v>-2.843793258029581</v>
+        <v>-3.573045488323814</v>
       </c>
       <c r="G26">
-        <v>-8.027527843386983</v>
+        <v>-7.650873835201943</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.9494728090915445</v>
       </c>
       <c r="E27">
-        <v>-19.56481665097261</v>
+        <v>-20.38896269257655</v>
       </c>
       <c r="F27">
-        <v>-3.191456299116426</v>
+        <v>-3.853784284836019</v>
       </c>
       <c r="G27">
-        <v>-7.550676863910361</v>
+        <v>-7.862887792627948</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.5650867968104663</v>
       </c>
       <c r="E28">
-        <v>-19.75215509219592</v>
+        <v>-20.81121119447376</v>
       </c>
       <c r="F28">
-        <v>-3.036437621142509</v>
+        <v>-3.975945024329356</v>
       </c>
       <c r="G28">
-        <v>-8.334961654891401</v>
+        <v>-8.234436939591433</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.22796367380798</v>
       </c>
       <c r="E29">
-        <v>-19.27378521192166</v>
+        <v>-19.18976843365735</v>
       </c>
       <c r="F29">
-        <v>-3.034890340463124</v>
+        <v>-3.672445998253413</v>
       </c>
       <c r="G29">
-        <v>-8.059093895103933</v>
+        <v>-9.297118747151943</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.02465039144674647</v>
       </c>
       <c r="E30">
-        <v>-19.24200890980983</v>
+        <v>-19.55442833159901</v>
       </c>
       <c r="F30">
-        <v>-2.699092424094752</v>
+        <v>-3.696770929261606</v>
       </c>
       <c r="G30">
-        <v>-8.239333236444015</v>
+        <v>-8.854760341648989</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1586203610764145</v>
       </c>
       <c r="E31">
-        <v>-19.12592600709721</v>
+        <v>-21.32619831557405</v>
       </c>
       <c r="F31">
-        <v>-2.927956933346738</v>
+        <v>-4.014865389054238</v>
       </c>
       <c r="G31">
-        <v>-8.585420977664963</v>
+        <v>-8.91607826612737</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.154386699589293</v>
       </c>
       <c r="E32">
-        <v>-19.1233810047049</v>
+        <v>-19.69898627887186</v>
       </c>
       <c r="F32">
-        <v>-3.152328468916621</v>
+        <v>-3.741764806172198</v>
       </c>
       <c r="G32">
-        <v>-8.268151535363369</v>
+        <v>-8.454654428863751</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.00202712626857629</v>
       </c>
       <c r="E33">
-        <v>-18.6736220232111</v>
+        <v>-19.3707534258479</v>
       </c>
       <c r="F33">
-        <v>-3.049514280886292</v>
+        <v>-4.200820970233307</v>
       </c>
       <c r="G33">
-        <v>-8.973181866134258</v>
+        <v>-8.434168773066741</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.2970336809905413</v>
       </c>
       <c r="E34">
-        <v>-19.69058143111363</v>
+        <v>-19.77804437809777</v>
       </c>
       <c r="F34">
-        <v>-3.343496818116359</v>
+        <v>-3.819876349333503</v>
       </c>
       <c r="G34">
-        <v>-7.889064276206965</v>
+        <v>-8.864228501891304</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.7260128249309837</v>
       </c>
       <c r="E35">
-        <v>-18.81866451720277</v>
+        <v>-19.11575052600197</v>
       </c>
       <c r="F35">
-        <v>-3.211992213721929</v>
+        <v>-4.373676927932819</v>
       </c>
       <c r="G35">
-        <v>-7.545174737224092</v>
+        <v>-8.875275792355852</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.267049069564315</v>
       </c>
       <c r="E36">
-        <v>-17.5673611078773</v>
+        <v>-19.60463552292205</v>
       </c>
       <c r="F36">
-        <v>-3.630222814841883</v>
+        <v>-4.388599396921047</v>
       </c>
       <c r="G36">
-        <v>-8.05397910224576</v>
+        <v>-8.6158647544441</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.889481258618675</v>
       </c>
       <c r="E37">
-        <v>-18.50293930938799</v>
+        <v>-18.57405446520445</v>
       </c>
       <c r="F37">
-        <v>-3.503634033608977</v>
+        <v>-4.637475614120525</v>
       </c>
       <c r="G37">
-        <v>-7.477811756591002</v>
+        <v>-7.907176270852318</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.566083456329108</v>
       </c>
       <c r="E38">
-        <v>-17.87694570493768</v>
+        <v>-17.64961178127862</v>
       </c>
       <c r="F38">
-        <v>-3.385535499788741</v>
+        <v>-4.59673319573993</v>
       </c>
       <c r="G38">
-        <v>-7.483631695649041</v>
+        <v>-8.221923077452987</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.267664149386099</v>
       </c>
       <c r="E39">
-        <v>-17.34841844655446</v>
+        <v>-18.959314391407</v>
       </c>
       <c r="F39">
-        <v>-3.286725712165601</v>
+        <v>-4.512270991857713</v>
       </c>
       <c r="G39">
-        <v>-7.387304752092867</v>
+        <v>-6.594640970351931</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.964710677639914</v>
       </c>
       <c r="E40">
-        <v>-17.03596732544722</v>
+        <v>-17.26400316257747</v>
       </c>
       <c r="F40">
-        <v>-3.539002145965528</v>
+        <v>-4.12040830237687</v>
       </c>
       <c r="G40">
-        <v>-7.307113407495101</v>
+        <v>-5.964465384769504</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.636052989123406</v>
       </c>
       <c r="E41">
-        <v>-17.13284044141931</v>
+        <v>-18.50422539600617</v>
       </c>
       <c r="F41">
-        <v>-3.371130110781904</v>
+        <v>-4.373146386451147</v>
       </c>
       <c r="G41">
-        <v>-7.110410723188225</v>
+        <v>-7.124318324998703</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.256376466781769</v>
       </c>
       <c r="E42">
-        <v>-16.61443432244323</v>
+        <v>-17.11056487777558</v>
       </c>
       <c r="F42">
-        <v>-3.488203195021892</v>
+        <v>-4.688753636103582</v>
       </c>
       <c r="G42">
-        <v>-7.167822203930266</v>
+        <v>-6.134839300402556</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.811125707240167</v>
       </c>
       <c r="E43">
-        <v>-16.37102884453095</v>
+        <v>-17.42792486470713</v>
       </c>
       <c r="F43">
-        <v>-3.632606292244619</v>
+        <v>-4.341232336696168</v>
       </c>
       <c r="G43">
-        <v>-6.510086326733406</v>
+        <v>-6.590857016800545</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.285436048542764</v>
       </c>
       <c r="E44">
-        <v>-15.79029280931329</v>
+        <v>-17.12233891019552</v>
       </c>
       <c r="F44">
-        <v>-3.579263909600788</v>
+        <v>-4.468494192943137</v>
       </c>
       <c r="G44">
-        <v>-6.90925204458549</v>
+        <v>-5.766047837873285</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.669081341454585</v>
       </c>
       <c r="E45">
-        <v>-15.93367788181816</v>
+        <v>-16.59587210748579</v>
       </c>
       <c r="F45">
-        <v>-3.794850628457728</v>
+        <v>-4.63436600755556</v>
       </c>
       <c r="G45">
-        <v>-6.026461971083435</v>
+        <v>-5.890107221411934</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.960002605965106</v>
       </c>
       <c r="E46">
-        <v>-14.72067177717556</v>
+        <v>-17.35018907989146</v>
       </c>
       <c r="F46">
-        <v>-3.756571664628599</v>
+        <v>-4.612776136663332</v>
       </c>
       <c r="G46">
-        <v>-5.477828432678796</v>
+        <v>-5.932786774504217</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>7.154888968365293</v>
       </c>
       <c r="E47">
-        <v>-14.12708846119815</v>
+        <v>-16.50917900108295</v>
       </c>
       <c r="F47">
-        <v>-4.013596048763014</v>
+        <v>-4.827711952389027</v>
       </c>
       <c r="G47">
-        <v>-6.128433394784066</v>
+        <v>-5.348617840281042</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>7.259796673617262</v>
       </c>
       <c r="E48">
-        <v>-14.68559421751215</v>
+        <v>-15.57715112319427</v>
       </c>
       <c r="F48">
-        <v>-3.945823729670656</v>
+        <v>-4.830028914143315</v>
       </c>
       <c r="G48">
-        <v>-5.410104602581925</v>
+        <v>-6.263884365523347</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>7.28044613103296</v>
       </c>
       <c r="E49">
-        <v>-13.5826028604119</v>
+        <v>-15.13593284367894</v>
       </c>
       <c r="F49">
-        <v>-4.198461248419303</v>
+        <v>-5.095751011165323</v>
       </c>
       <c r="G49">
-        <v>-5.301611404168931</v>
+        <v>-5.586702343828808</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>7.22237686719982</v>
       </c>
       <c r="E50">
-        <v>-13.04512733738952</v>
+        <v>-14.63636064810076</v>
       </c>
       <c r="F50">
-        <v>-4.226501553505115</v>
+        <v>-4.892236090648819</v>
       </c>
       <c r="G50">
-        <v>-4.814090536419237</v>
+        <v>-5.5615719926402</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>7.097091685305186</v>
       </c>
       <c r="E51">
-        <v>-13.19946226004493</v>
+        <v>-15.11394257389769</v>
       </c>
       <c r="F51">
-        <v>-4.185358457527914</v>
+        <v>-4.91708602016798</v>
       </c>
       <c r="G51">
-        <v>-4.219132534283577</v>
+        <v>-4.836228154440344</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>6.910477103612373</v>
       </c>
       <c r="E52">
-        <v>-13.26925962992515</v>
+        <v>-14.74445532266385</v>
       </c>
       <c r="F52">
-        <v>-4.49625655764079</v>
+        <v>-5.110553118503978</v>
       </c>
       <c r="G52">
-        <v>-4.670230780010208</v>
+        <v>-4.810783301425506</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>6.672333132699211</v>
       </c>
       <c r="E53">
-        <v>-13.53780719552802</v>
+        <v>-15.47907343313615</v>
       </c>
       <c r="F53">
-        <v>-4.513495196530348</v>
+        <v>-5.023450876860724</v>
       </c>
       <c r="G53">
-        <v>-4.913870378972871</v>
+        <v>-4.355149608310072</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>6.390731476293571</v>
       </c>
       <c r="E54">
-        <v>-13.55667734671798</v>
+        <v>-13.47543652302038</v>
       </c>
       <c r="F54">
-        <v>-4.827790345831842</v>
+        <v>-5.090120144782978</v>
       </c>
       <c r="G54">
-        <v>-4.370143069057432</v>
+        <v>-4.981713388709156</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>6.068171010496499</v>
       </c>
       <c r="E55">
-        <v>-11.68395862016396</v>
+        <v>-14.3910215117872</v>
       </c>
       <c r="F55">
-        <v>-4.657317865535067</v>
+        <v>-5.533605312283487</v>
       </c>
       <c r="G55">
-        <v>-3.977929496837817</v>
+        <v>-4.473041445509059</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>5.713331526686788</v>
       </c>
       <c r="E56">
-        <v>-12.24193001654506</v>
+        <v>-11.9481769646155</v>
       </c>
       <c r="F56">
-        <v>-4.773390047636497</v>
+        <v>-5.339091384337383</v>
       </c>
       <c r="G56">
-        <v>-3.730370211956657</v>
+        <v>-4.455879577433477</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>5.327274764493392</v>
       </c>
       <c r="E57">
-        <v>-12.63092140532993</v>
+        <v>-12.48393166751496</v>
       </c>
       <c r="F57">
-        <v>-4.700209372842913</v>
+        <v>-5.444714274808743</v>
       </c>
       <c r="G57">
-        <v>-4.700409713146204</v>
+        <v>-4.938851755612212</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>4.915877536836263</v>
       </c>
       <c r="E58">
-        <v>-11.57401179973173</v>
+        <v>-13.19482057418707</v>
       </c>
       <c r="F58">
-        <v>-4.893061201430763</v>
+        <v>-5.498497719550024</v>
       </c>
       <c r="G58">
-        <v>-4.718475360154007</v>
+        <v>-5.073955119069868</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>4.485758854168805</v>
       </c>
       <c r="E59">
-        <v>-11.4231502166402</v>
+        <v>-12.28919369976311</v>
       </c>
       <c r="F59">
-        <v>-4.597214642338224</v>
+        <v>-5.802975475881709</v>
       </c>
       <c r="G59">
-        <v>-3.859471556351616</v>
+        <v>-4.961813699472597</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>4.040631525106834</v>
       </c>
       <c r="E60">
-        <v>-12.24640867733864</v>
+        <v>-12.52664423435531</v>
       </c>
       <c r="F60">
-        <v>-4.94685335655458</v>
+        <v>-5.426291023894437</v>
       </c>
       <c r="G60">
-        <v>-5.196144044378829</v>
+        <v>-5.535849053800063</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>3.593887670709833</v>
       </c>
       <c r="E61">
-        <v>-11.33494912839281</v>
+        <v>-12.31720231150055</v>
       </c>
       <c r="F61">
-        <v>-5.038641784001618</v>
+        <v>-5.922226155755427</v>
       </c>
       <c r="G61">
-        <v>-4.727033120373023</v>
+        <v>-5.007873319560477</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>3.153259876563068</v>
       </c>
       <c r="E62">
-        <v>-11.43069465433698</v>
+        <v>-11.5160156331155</v>
       </c>
       <c r="F62">
-        <v>-5.048443339912273</v>
+        <v>-5.75021193774997</v>
       </c>
       <c r="G62">
-        <v>-4.955434278218421</v>
+        <v>-5.651099075658711</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>2.734086633452236</v>
       </c>
       <c r="E63">
-        <v>-11.44216527899841</v>
+        <v>-11.48848251114886</v>
       </c>
       <c r="F63">
-        <v>-5.130472971508375</v>
+        <v>-5.643965067147927</v>
       </c>
       <c r="G63">
-        <v>-4.504170505214826</v>
+        <v>-5.687915652600946</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.351228342991319</v>
       </c>
       <c r="E64">
-        <v>-10.51993701886233</v>
+        <v>-11.74293746563986</v>
       </c>
       <c r="F64">
-        <v>-5.306420323154825</v>
+        <v>-5.986450181744242</v>
       </c>
       <c r="G64">
-        <v>-5.058402176126372</v>
+        <v>-5.916690902092281</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.018075312222554</v>
       </c>
       <c r="E65">
-        <v>-11.05920128911774</v>
+        <v>-12.821656202059</v>
       </c>
       <c r="F65">
-        <v>-5.24960645714435</v>
+        <v>-5.690738237654515</v>
       </c>
       <c r="G65">
-        <v>-5.858637175515621</v>
+        <v>-4.808813526829639</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.752970430361538</v>
       </c>
       <c r="E66">
-        <v>-11.08144968191743</v>
+        <v>-12.45143533803592</v>
       </c>
       <c r="F66">
-        <v>-5.36074064420144</v>
+        <v>-5.693402822857242</v>
       </c>
       <c r="G66">
-        <v>-4.693454256968195</v>
+        <v>-6.089792707249693</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.562921083879859</v>
       </c>
       <c r="E67">
-        <v>-11.31928513680027</v>
+        <v>-12.25557883720417</v>
       </c>
       <c r="F67">
-        <v>-5.245434975763082</v>
+        <v>-6.089979412995392</v>
       </c>
       <c r="G67">
-        <v>-5.707351865462007</v>
+        <v>-5.889094194476916</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.457340388277819</v>
       </c>
       <c r="E68">
-        <v>-11.13808730633136</v>
+        <v>-12.6033928118373</v>
       </c>
       <c r="F68">
-        <v>-5.491637897377299</v>
+        <v>-6.479508511809836</v>
       </c>
       <c r="G68">
-        <v>-5.379031822150326</v>
+        <v>-6.471339701741776</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.435549290949764</v>
       </c>
       <c r="E69">
-        <v>-10.86294628257332</v>
+        <v>-10.56396737163891</v>
       </c>
       <c r="F69">
-        <v>-5.054721942014033</v>
+        <v>-6.264630105423575</v>
       </c>
       <c r="G69">
-        <v>-4.502545027355044</v>
+        <v>-5.820363958536108</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.493801905288507</v>
       </c>
       <c r="E70">
-        <v>-11.42190035781408</v>
+        <v>-11.61008562367683</v>
       </c>
       <c r="F70">
-        <v>-5.331605998328058</v>
+        <v>-6.157610386334797</v>
       </c>
       <c r="G70">
-        <v>-5.825684005217716</v>
+        <v>-5.572692115106612</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.6283854988991</v>
       </c>
       <c r="E71">
-        <v>-11.94950380749974</v>
+        <v>-11.0358570056082</v>
       </c>
       <c r="F71">
-        <v>-5.442953193830775</v>
+        <v>-6.267183831212221</v>
       </c>
       <c r="G71">
-        <v>-4.614981085505311</v>
+        <v>-6.881115718047224</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.828377227666384</v>
       </c>
       <c r="E72">
-        <v>-11.84126875024241</v>
+        <v>-12.9619302129206</v>
       </c>
       <c r="F72">
-        <v>-5.310821441893831</v>
+        <v>-6.354599646626733</v>
       </c>
       <c r="G72">
-        <v>-5.520759587232065</v>
+        <v>-5.219907140259718</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>2.08844874331333</v>
       </c>
       <c r="E73">
-        <v>-12.03369266777634</v>
+        <v>-11.69322387798365</v>
       </c>
       <c r="F73">
-        <v>-5.537454509510962</v>
+        <v>-6.22130743418025</v>
       </c>
       <c r="G73">
-        <v>-5.511940293915447</v>
+        <v>-6.874494626968682</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.394203686746253</v>
       </c>
       <c r="E74">
-        <v>-11.85746710176785</v>
+        <v>-12.89489068371105</v>
       </c>
       <c r="F74">
-        <v>-5.377938898590155</v>
+        <v>-6.413409773943619</v>
       </c>
       <c r="G74">
-        <v>-5.079073222473582</v>
+        <v>-6.080304683734142</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.732581458268672</v>
       </c>
       <c r="E75">
-        <v>-13.12798029783385</v>
+        <v>-12.8540664905319</v>
       </c>
       <c r="F75">
-        <v>-5.451262898769086</v>
+        <v>-6.240452854991998</v>
       </c>
       <c r="G75">
-        <v>-5.34471801763578</v>
+        <v>-5.861838473052097</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>3.087679155016105</v>
       </c>
       <c r="E76">
-        <v>-13.45052085903017</v>
+        <v>-14.2426007761858</v>
       </c>
       <c r="F76">
-        <v>-5.650081339393354</v>
+        <v>-6.63601824890314</v>
       </c>
       <c r="G76">
-        <v>-4.899227836052675</v>
+        <v>-5.481698460414204</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.440035076150052</v>
       </c>
       <c r="E77">
-        <v>-13.01882143187896</v>
+        <v>-14.37992675046841</v>
       </c>
       <c r="F77">
-        <v>-5.806479425219619</v>
+        <v>-6.352866676428763</v>
       </c>
       <c r="G77">
-        <v>-5.315184640879942</v>
+        <v>-6.356589572259558</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.774392426709023</v>
       </c>
       <c r="E78">
-        <v>-13.72846047972495</v>
+        <v>-15.04175416974141</v>
       </c>
       <c r="F78">
-        <v>-5.861953476025632</v>
+        <v>-6.82818908394735</v>
       </c>
       <c r="G78">
-        <v>-4.497820878870503</v>
+        <v>-5.761694470489143</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.071180065268211</v>
       </c>
       <c r="E79">
-        <v>-14.95853440290246</v>
+        <v>-15.54729942253571</v>
       </c>
       <c r="F79">
-        <v>-5.933665263582645</v>
+        <v>-6.378861625324786</v>
       </c>
       <c r="G79">
-        <v>-4.885767157889997</v>
+        <v>-5.544886843122273</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>4.317085843674616</v>
       </c>
       <c r="E80">
-        <v>-14.21480047425272</v>
+        <v>-14.77179824872216</v>
       </c>
       <c r="F80">
-        <v>-6.320571745401121</v>
+        <v>-6.855731313522758</v>
       </c>
       <c r="G80">
-        <v>-5.220056114808984</v>
+        <v>-5.966196800086543</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>4.501120478120903</v>
       </c>
       <c r="E81">
-        <v>-15.43295545384203</v>
+        <v>-15.57837833965035</v>
       </c>
       <c r="F81">
-        <v>-6.116184994778169</v>
+        <v>-6.688585011574885</v>
       </c>
       <c r="G81">
-        <v>-5.422942898183219</v>
+        <v>-5.566988045142448</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>4.618749396157471</v>
       </c>
       <c r="E82">
-        <v>-16.25395873448466</v>
+        <v>-16.69538985227835</v>
       </c>
       <c r="F82">
-        <v>-6.267617766633052</v>
+        <v>-6.853563616051001</v>
       </c>
       <c r="G82">
-        <v>-4.536862142415129</v>
+        <v>-6.38206422018425</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>4.676501032960559</v>
       </c>
       <c r="E83">
-        <v>-17.53401795375883</v>
+        <v>-17.43263900614911</v>
       </c>
       <c r="F83">
-        <v>-6.069058657852437</v>
+        <v>-7.100777337965746</v>
       </c>
       <c r="G83">
-        <v>-5.112579253876546</v>
+        <v>-5.751362257861078</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.680927226359252</v>
       </c>
       <c r="E84">
-        <v>-18.31988933304994</v>
+        <v>-18.76519682459421</v>
       </c>
       <c r="F84">
-        <v>-6.133053442409993</v>
+        <v>-6.871924706508127</v>
       </c>
       <c r="G84">
-        <v>-4.985424510258678</v>
+        <v>-6.323808550329694</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.639968769600215</v>
       </c>
       <c r="E85">
-        <v>-19.13832496893021</v>
+        <v>-18.91673767878689</v>
       </c>
       <c r="F85">
-        <v>-6.370875788246183</v>
+        <v>-6.917970955999528</v>
       </c>
       <c r="G85">
-        <v>-4.836148701347401</v>
+        <v>-6.17792936114171</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.557027216148762</v>
       </c>
       <c r="E86">
-        <v>-20.18022721166699</v>
+        <v>-21.21155999606987</v>
       </c>
       <c r="F86">
-        <v>-6.419502290600314</v>
+        <v>-7.281180842131763</v>
       </c>
       <c r="G86">
-        <v>-4.814650018615374</v>
+        <v>-6.08944178942253</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.431732551870152</v>
       </c>
       <c r="E87">
-        <v>-22.11379051498808</v>
+        <v>-22.81476206358338</v>
       </c>
       <c r="F87">
-        <v>-6.398707836004116</v>
+        <v>-7.190822105199887</v>
       </c>
       <c r="G87">
-        <v>-4.532108199020736</v>
+        <v>-6.397660200219756</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.266522190623014</v>
       </c>
       <c r="E88">
-        <v>-23.38735137406124</v>
+        <v>-22.86547644399528</v>
       </c>
       <c r="F88">
-        <v>-6.673945630019041</v>
+        <v>-7.223709342239903</v>
       </c>
       <c r="G88">
-        <v>-4.691193154364873</v>
+        <v>-5.771996888207355</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.060609418149239</v>
       </c>
       <c r="E89">
-        <v>-24.55738226037105</v>
+        <v>-24.41432776646874</v>
       </c>
       <c r="F89">
-        <v>-6.525990676354462</v>
+        <v>-7.170546710217473</v>
       </c>
       <c r="G89">
-        <v>-4.752325688293054</v>
+        <v>-5.500419595438783</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.814451102675135</v>
       </c>
       <c r="E90">
-        <v>-26.05450482425488</v>
+        <v>-25.82436777518507</v>
       </c>
       <c r="F90">
-        <v>-6.518123617219517</v>
+        <v>-7.306575170559356</v>
       </c>
       <c r="G90">
-        <v>-4.479775095135937</v>
+        <v>-5.861020768303897</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.528722785225145</v>
       </c>
       <c r="E91">
-        <v>-27.21217750499775</v>
+        <v>-27.7081857915319</v>
       </c>
       <c r="F91">
-        <v>-6.44244741782968</v>
+        <v>-6.834116103335883</v>
       </c>
       <c r="G91">
-        <v>-4.907044034070894</v>
+        <v>-5.580405686213114</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.200095184754702</v>
       </c>
       <c r="E92">
-        <v>-28.93215986022107</v>
+        <v>-29.5692640756492</v>
       </c>
       <c r="F92">
-        <v>-6.686097801434687</v>
+        <v>-7.144223934196954</v>
       </c>
       <c r="G92">
-        <v>-4.875236312529577</v>
+        <v>-6.398444799512563</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.830446795295885</v>
       </c>
       <c r="E93">
-        <v>-30.40478790819742</v>
+        <v>-31.52587504743232</v>
       </c>
       <c r="F93">
-        <v>-6.808515101286325</v>
+        <v>-7.012948967160263</v>
       </c>
       <c r="G93">
-        <v>-5.531565207872246</v>
+        <v>-5.736719714940882</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.420360808926149</v>
       </c>
       <c r="E94">
-        <v>-32.68869886735892</v>
+        <v>-32.94750794960829</v>
       </c>
       <c r="F94">
-        <v>-6.769759441976649</v>
+        <v>-7.315368697654834</v>
       </c>
       <c r="G94">
-        <v>-5.3395436349579</v>
+        <v>-5.46032226786713</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.974214188555422</v>
       </c>
       <c r="E95">
-        <v>-36.09280032790181</v>
+        <v>-35.24953733327448</v>
       </c>
       <c r="F95">
-        <v>-6.408692309948004</v>
+        <v>-6.992520348630531</v>
       </c>
       <c r="G95">
-        <v>-6.092871514601216</v>
+        <v>-7.924665882936288</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.494898259074073</v>
       </c>
       <c r="E96">
-        <v>-37.45335090842531</v>
+        <v>-38.13891432420953</v>
       </c>
       <c r="F96">
-        <v>-6.784361606443479</v>
+        <v>-6.987736764912945</v>
       </c>
       <c r="G96">
-        <v>-6.297400328562929</v>
+        <v>-6.695629162027399</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.9915615486380912</v>
       </c>
       <c r="E97">
-        <v>-38.73602532143892</v>
+        <v>-39.4867489497195</v>
       </c>
       <c r="F97">
-        <v>-6.683665625075051</v>
+        <v>-6.884940789500645</v>
       </c>
       <c r="G97">
-        <v>-6.63807532782717</v>
+        <v>-7.296195228306585</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.461348839274248</v>
       </c>
       <c r="E98">
-        <v>-41.62463247179266</v>
+        <v>-42.7091952039187</v>
       </c>
       <c r="F98">
-        <v>-6.178221131044805</v>
+        <v>-7.448029803294013</v>
       </c>
       <c r="G98">
-        <v>-7.17007668544251</v>
+        <v>-8.719640425463634</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.07265505314986584</v>
       </c>
       <c r="E99">
-        <v>-43.22419364620401</v>
+        <v>-44.73961350931583</v>
       </c>
       <c r="F99">
-        <v>-6.656001846070633</v>
+        <v>-6.658971690588561</v>
       </c>
       <c r="G99">
-        <v>-7.809015285067388</v>
+        <v>-8.529595248236234</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.6312758903491491</v>
       </c>
       <c r="E100">
-        <v>-45.99137429451608</v>
+        <v>-45.98937497324169</v>
       </c>
       <c r="F100">
-        <v>-6.392419335740384</v>
+        <v>-6.989716397307245</v>
       </c>
       <c r="G100">
-        <v>-9.114836799214133</v>
+        <v>-8.884575114775664</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.161232721002686</v>
       </c>
       <c r="E101">
-        <v>-48.17607544511753</v>
+        <v>-48.39082247527227</v>
       </c>
       <c r="F101">
-        <v>-6.636250261819751</v>
+        <v>-6.469421492907923</v>
       </c>
       <c r="G101">
-        <v>-8.553434486664525</v>
+        <v>-9.396289449326352</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.730913576118446</v>
       </c>
       <c r="E102">
-        <v>-51.26207990958413</v>
+        <v>-50.7167214454329</v>
       </c>
       <c r="F102">
-        <v>-6.137583237254629</v>
+        <v>-6.228220310501143</v>
       </c>
       <c r="G102">
-        <v>-9.123897762355119</v>
+        <v>-9.470647612683921</v>
       </c>
     </row>
   </sheetData>
